--- a/mart_price.xlsx
+++ b/mart_price.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>상품 이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,6 +94,38 @@
   </si>
   <si>
     <t>마트 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참외</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이스마트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블루베리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이스마트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>200g</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4개</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -424,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.25" customWidth="1"/>
@@ -578,6 +610,75 @@
         <v>4000</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>2025</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>4500</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>2025</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>6200</v>
+      </c>
+      <c r="G9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>2025</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1980</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/mart_price.xlsx
+++ b/mart_price.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>상품 이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -69,10 +69,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>가격(원)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>에이스마트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -126,6 +122,38 @@
   </si>
   <si>
     <t>4개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돼지고기 앞다리살</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>월마트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양파(1망)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참외</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대파</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1단</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕자반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -133,6 +161,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -172,8 +203,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.25" customWidth="1"/>
@@ -469,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -481,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -503,7 +537,7 @@
       <c r="E2">
         <v>30</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>3860</v>
       </c>
       <c r="G2" t="s">
@@ -526,16 +560,16 @@
       <c r="E3">
         <v>30</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>5600</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>2025</v>
@@ -546,13 +580,13 @@
       <c r="E4">
         <v>30</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>4250</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -566,13 +600,13 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>3800</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -586,13 +620,13 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>5500</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -606,59 +640,59 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>4000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8">
+        <v>2025</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4500</v>
+      </c>
+      <c r="G8" t="s">
         <v>18</v>
-      </c>
-      <c r="C8">
-        <v>2025</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>4500</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9">
+        <v>2025</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6200</v>
+      </c>
+      <c r="G9" t="s">
         <v>21</v>
-      </c>
-      <c r="C9">
-        <v>2025</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>6200</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -672,16 +706,120 @@
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>1980</v>
       </c>
       <c r="G10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>2025</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12">
+        <v>2025</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>2025</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>2025</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15">
+        <v>2025</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>13900</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G5"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/mart_price.xlsx
+++ b/mart_price.xlsx
@@ -69,6 +69,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>가격(원)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>에이스마트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,10 +154,6 @@
   </si>
   <si>
     <t>왕자반</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가격</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -503,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -515,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
       </c>
       <c r="C4">
         <v>2025</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -606,7 +606,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -646,10 +646,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8">
         <v>2025</v>
@@ -664,15 +664,15 @@
         <v>4500</v>
       </c>
       <c r="G8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>2025</v>
@@ -687,12 +687,12 @@
         <v>6200</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -710,15 +710,15 @@
         <v>1980</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>2025</v>
@@ -735,10 +735,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
       </c>
       <c r="C12">
         <v>2025</v>
@@ -755,10 +755,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>2025</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>2025</v>
@@ -793,15 +793,15 @@
         <v>1500</v>
       </c>
       <c r="G14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15">
         <v>2025</v>
